--- a/data/processed/positivacao/2021-04_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2021-04_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -24503,7 +24503,7 @@
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B930" t="inlineStr"/>
@@ -36063,7 +36063,7 @@
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1375" t="inlineStr"/>
@@ -64851,7 +64851,7 @@
     <row r="2483">
       <c r="A2483" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2483" t="inlineStr"/>
@@ -66522,12 +66522,12 @@
       <c r="A2548" t="inlineStr"/>
       <c r="B2548" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 0 cliente(s), não positivou 91 cliente(s) - Total vendido: R$ 0,00
+          <t>Vendedor 1 - VENDEDOR 01: positivou 0 cliente(s), não positivou 91 cliente(s) - Total vendido: R$ 0,00
 Vendedor 18 - LOJA: positivou 54 cliente(s), não positivou 775 cliente(s) - Total vendido: R$ 91.234,90
-Vendedor 3 - FERNANDA: positivou 84 cliente(s), não positivou 360 cliente(s) - Total vendido: R$ 71.829,96
-Vendedor 4 - DANIELA: positivou 0 cliente(s), não positivou 653 cliente(s) - Total vendido: R$ 0,00
+Vendedor 3 - VENDEDOR 03: positivou 84 cliente(s), não positivou 360 cliente(s) - Total vendido: R$ 71.829,96
+Vendedor 4 - VENDEDOR 04: positivou 0 cliente(s), não positivou 653 cliente(s) - Total vendido: R$ 0,00
 Vendedor 5 - SITE: positivou 0 cliente(s), não positivou 453 cliente(s) - Total vendido: R$ 0,00
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2548" t="inlineStr"/>
